--- a/seminar_02/problem_2.16_solution.xlsx
+++ b/seminar_02/problem_2.16_solution.xlsx
@@ -1054,9 +1054,10 @@
         <f>COUNT(Данные!$D$7:$D$23)</f>
         <v/>
       </c>
-      <c r="C5" s="13">
-        <f>СЧЁТ(столбец δw)</f>
-        <v/>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>=СЧЁТ(столбец δw)</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -1069,9 +1070,10 @@
         <f>AVERAGE(Данные!$E$7:$E$23)</f>
         <v/>
       </c>
-      <c r="C6" s="13">
-        <f>СРЗНАЧ(столбец z)</f>
-        <v/>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>=СРЗНАЧ(столбец z)</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1084,9 +1086,10 @@
         <f>AVERAGE(Данные!$D$7:$D$23)</f>
         <v/>
       </c>
-      <c r="C7" s="13">
-        <f>СРЗНАЧ(столбец δw)</f>
-        <v/>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>=СРЗНАЧ(столбец δw)</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1099,9 +1102,10 @@
         <f>DEVSQ(Данные!$E$7:$E$23)</f>
         <v/>
       </c>
-      <c r="C8" s="13">
-        <f>КВАДРОТКЛ(столбец z)</f>
-        <v/>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>=КВАДРОТКЛ(столбец z)</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1114,9 +1118,10 @@
         <f>SUMPRODUCT(Данные!$E$7:$E$23-B6,Данные!$D$7:$D$23-B7)</f>
         <v/>
       </c>
-      <c r="C9" s="13">
-        <f>СУММПРОИЗВ(z − z̄; δw − δw̄)</f>
-        <v/>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>=СУММПРОИЗВ(z − z̄; δw − δw̄)</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -1129,9 +1134,10 @@
         <f>DEVSQ(Данные!$D$7:$D$23)</f>
         <v/>
       </c>
-      <c r="C10" s="13">
-        <f>КВАДРОТКЛ(столбец δw)</f>
-        <v/>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>=КВАДРОТКЛ(столбец δw)</t>
+        </is>
       </c>
     </row>
     <row r="11"/>
@@ -1858,9 +1864,10 @@
         <f>TDIST(ABS(B51),B47,2)</f>
         <v/>
       </c>
-      <c r="C53" s="13">
-        <f>СТЬЮДРАСП(|t|; n − 2; 2)</f>
-        <v/>
+      <c r="C53" s="13" t="inlineStr">
+        <is>
+          <t>=СТЬЮДРАСП(|t|; n − 2; 2)</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -1873,9 +1880,10 @@
         <f>TDIST(ABS(B52),B47,2)</f>
         <v/>
       </c>
-      <c r="C54" s="13">
-        <f>СТЬЮДРАСП(|t|; n − 2; 2)</f>
-        <v/>
+      <c r="C54" s="13" t="inlineStr">
+        <is>
+          <t>=СТЬЮДРАСП(|t|; n − 2; 2)</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -1921,9 +1929,10 @@
         <f>FDIST(B57,1,B47)</f>
         <v/>
       </c>
-      <c r="C58" s="13">
-        <f>FРАСП(F; 1; n − 2)</f>
-        <v/>
+      <c r="C58" s="13" t="inlineStr">
+        <is>
+          <t>=FРАСП(F; 1; n − 2)</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -2790,9 +2799,10 @@
         <f>TINV(B5,B4)</f>
         <v/>
       </c>
-      <c r="C6" s="13">
-        <f>СТЬЮДРАСПОБР(уровень; n − 2)</f>
-        <v/>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>=СТЬЮДРАСПОБР(уровень; n − 2)</t>
+        </is>
       </c>
     </row>
     <row r="7"/>
